--- a/Team-Data/2014-15/12-24-2014-15.xlsx
+++ b/Team-Data/2014-15/12-24-2014-15.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>5.9</v>
       </c>
       <c r="AD2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AE2" t="n">
         <v>4</v>
@@ -769,7 +836,7 @@
         <v>9</v>
       </c>
       <c r="AN2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO2" t="n">
         <v>14</v>
@@ -799,7 +866,7 @@
         <v>7</v>
       </c>
       <c r="AX2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY2" t="n">
         <v>11</v>
@@ -808,7 +875,7 @@
         <v>4</v>
       </c>
       <c r="BA2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BB2" t="n">
         <v>9</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>12-24-2014-15</t>
+          <t>2014-12-24</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>-0.7</v>
       </c>
       <c r="AD3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
         <v>22</v>
@@ -942,7 +1009,7 @@
         <v>1</v>
       </c>
       <c r="AK3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL3" t="n">
         <v>15</v>
@@ -960,7 +1027,7 @@
         <v>26</v>
       </c>
       <c r="AQ3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR3" t="n">
         <v>15</v>
@@ -975,7 +1042,7 @@
         <v>2</v>
       </c>
       <c r="AV3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW3" t="n">
         <v>8</v>
@@ -996,7 +1063,7 @@
         <v>7</v>
       </c>
       <c r="BC3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>12-24-2014-15</t>
+          <t>2014-12-24</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-2</v>
       </c>
       <c r="AD4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AE4" t="n">
         <v>18</v>
@@ -1118,7 +1185,7 @@
         <v>4</v>
       </c>
       <c r="AI4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ4" t="n">
         <v>19</v>
@@ -1133,7 +1200,7 @@
         <v>18</v>
       </c>
       <c r="AN4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO4" t="n">
         <v>25</v>
@@ -1157,7 +1224,7 @@
         <v>15</v>
       </c>
       <c r="AV4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW4" t="n">
         <v>18</v>
@@ -1169,7 +1236,7 @@
         <v>13</v>
       </c>
       <c r="AZ4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA4" t="n">
         <v>23</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>12-24-2014-15</t>
+          <t>2014-12-24</t>
         </is>
       </c>
     </row>
@@ -1285,13 +1352,13 @@
         <v>-3.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE5" t="n">
         <v>22</v>
       </c>
       <c r="AF5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG5" t="n">
         <v>23</v>
@@ -1303,7 +1370,7 @@
         <v>18</v>
       </c>
       <c r="AJ5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AK5" t="n">
         <v>25</v>
@@ -1312,7 +1379,7 @@
         <v>26</v>
       </c>
       <c r="AM5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AN5" t="n">
         <v>25</v>
@@ -1330,7 +1397,7 @@
         <v>26</v>
       </c>
       <c r="AS5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT5" t="n">
         <v>19</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>12-24-2014-15</t>
+          <t>2014-12-24</t>
         </is>
       </c>
     </row>
@@ -1467,19 +1534,19 @@
         <v>4.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AE6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF6" t="n">
         <v>8</v>
       </c>
       <c r="AG6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI6" t="n">
         <v>19</v>
@@ -1539,7 +1606,7 @@
         <v>2</v>
       </c>
       <c r="BB6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BC6" t="n">
         <v>9</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>12-24-2014-15</t>
+          <t>2014-12-24</t>
         </is>
       </c>
     </row>
@@ -1649,13 +1716,13 @@
         <v>4.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AE7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG7" t="n">
         <v>11</v>
@@ -1685,19 +1752,19 @@
         <v>5</v>
       </c>
       <c r="AP7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AQ7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR7" t="n">
         <v>19</v>
       </c>
       <c r="AS7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AU7" t="n">
         <v>8</v>
@@ -1718,7 +1785,7 @@
         <v>1</v>
       </c>
       <c r="BA7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BB7" t="n">
         <v>8</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>12-24-2014-15</t>
+          <t>2014-12-24</t>
         </is>
       </c>
     </row>
@@ -1753,67 +1820,67 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E8" t="n">
         <v>20</v>
       </c>
       <c r="F8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.667</v>
       </c>
       <c r="H8" t="n">
         <v>48.5</v>
       </c>
       <c r="I8" t="n">
-        <v>41.2</v>
+        <v>41.1</v>
       </c>
       <c r="J8" t="n">
-        <v>86.40000000000001</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>0.476</v>
+        <v>0.477</v>
       </c>
       <c r="L8" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>27.4</v>
+        <v>27.2</v>
       </c>
       <c r="N8" t="n">
-        <v>0.354</v>
+        <v>0.355</v>
       </c>
       <c r="O8" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="P8" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.768</v>
+        <v>0.77</v>
       </c>
       <c r="R8" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="S8" t="n">
-        <v>31.1</v>
+        <v>30.9</v>
       </c>
       <c r="T8" t="n">
-        <v>42.7</v>
+        <v>42.3</v>
       </c>
       <c r="U8" t="n">
-        <v>23.6</v>
+        <v>23.4</v>
       </c>
       <c r="V8" t="n">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="W8" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="X8" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Y8" t="n">
         <v>3.4</v>
@@ -1822,28 +1889,28 @@
         <v>20.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>110</v>
+        <v>109.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE8" t="n">
         <v>6</v>
       </c>
       <c r="AF8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AI8" t="n">
         <v>1</v>
@@ -1858,7 +1925,7 @@
         <v>4</v>
       </c>
       <c r="AM8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN8" t="n">
         <v>16</v>
@@ -1870,16 +1937,16 @@
         <v>16</v>
       </c>
       <c r="AQ8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT8" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AU8" t="n">
         <v>7</v>
@@ -1894,7 +1961,7 @@
         <v>10</v>
       </c>
       <c r="AY8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AZ8" t="n">
         <v>13</v>
@@ -1906,7 +1973,7 @@
         <v>1</v>
       </c>
       <c r="BC8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>12-24-2014-15</t>
+          <t>2014-12-24</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>-2.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE9" t="n">
         <v>18</v>
@@ -2046,7 +2113,7 @@
         <v>28</v>
       </c>
       <c r="AO9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AP9" t="n">
         <v>9</v>
@@ -2076,13 +2143,13 @@
         <v>16</v>
       </c>
       <c r="AY9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AZ9" t="n">
         <v>30</v>
       </c>
       <c r="BA9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BB9" t="n">
         <v>16</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>12-24-2014-15</t>
+          <t>2014-12-24</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-6.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AE10" t="n">
         <v>27</v>
@@ -2207,13 +2274,13 @@
         <v>28</v>
       </c>
       <c r="AH10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI10" t="n">
         <v>27</v>
       </c>
       <c r="AJ10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK10" t="n">
         <v>30</v>
@@ -2243,7 +2310,7 @@
         <v>14</v>
       </c>
       <c r="AT10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AU10" t="n">
         <v>23</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>12-24-2014-15</t>
+          <t>2014-12-24</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>9.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2395,13 +2462,13 @@
         <v>2</v>
       </c>
       <c r="AJ11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AK11" t="n">
         <v>1</v>
       </c>
       <c r="AL11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AM11" t="n">
         <v>5</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>12-24-2014-15</t>
+          <t>2014-12-24</t>
         </is>
       </c>
     </row>
@@ -2481,25 +2548,25 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F12" t="n">
         <v>7</v>
       </c>
       <c r="G12" t="n">
-        <v>0.731</v>
+        <v>0.741</v>
       </c>
       <c r="H12" t="n">
         <v>48.6</v>
       </c>
       <c r="I12" t="n">
-        <v>35</v>
+        <v>34.9</v>
       </c>
       <c r="J12" t="n">
-        <v>82.40000000000001</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K12" t="n">
         <v>0.425</v>
@@ -2508,61 +2575,61 @@
         <v>11.7</v>
       </c>
       <c r="M12" t="n">
-        <v>34.4</v>
+        <v>34.2</v>
       </c>
       <c r="N12" t="n">
-        <v>0.34</v>
+        <v>0.342</v>
       </c>
       <c r="O12" t="n">
-        <v>18</v>
+        <v>18.6</v>
       </c>
       <c r="P12" t="n">
-        <v>25.2</v>
+        <v>26.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.717</v>
+        <v>0.714</v>
       </c>
       <c r="R12" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="S12" t="n">
         <v>32.2</v>
       </c>
       <c r="T12" t="n">
-        <v>44.4</v>
+        <v>44.5</v>
       </c>
       <c r="U12" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="V12" t="n">
-        <v>17.3</v>
+        <v>17.1</v>
       </c>
       <c r="W12" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="X12" t="n">
         <v>5</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Z12" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AD12" t="n">
         <v>23</v>
       </c>
-      <c r="AA12" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>99.8</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>29</v>
-      </c>
       <c r="AE12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF12" t="n">
         <v>2</v>
@@ -2571,7 +2638,7 @@
         <v>6</v>
       </c>
       <c r="AH12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI12" t="n">
         <v>28</v>
@@ -2592,10 +2659,10 @@
         <v>18</v>
       </c>
       <c r="AO12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AP12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AQ12" t="n">
         <v>28</v>
@@ -2619,22 +2686,22 @@
         <v>3</v>
       </c>
       <c r="AX12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY12" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AZ12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BA12" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="BB12" t="n">
         <v>18</v>
       </c>
       <c r="BC12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>12-24-2014-15</t>
+          <t>2014-12-24</t>
         </is>
       </c>
     </row>
@@ -2741,13 +2808,13 @@
         <v>-2.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE13" t="n">
         <v>22</v>
       </c>
       <c r="AF13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG13" t="n">
         <v>23</v>
@@ -2765,7 +2832,7 @@
         <v>27</v>
       </c>
       <c r="AL13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AM13" t="n">
         <v>17</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>12-24-2014-15</t>
+          <t>2014-12-24</t>
         </is>
       </c>
     </row>
@@ -2923,13 +2990,13 @@
         <v>5.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG14" t="n">
         <v>10</v>
@@ -2953,16 +3020,16 @@
         <v>4</v>
       </c>
       <c r="AN14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AP14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR14" t="n">
         <v>28</v>
@@ -2977,13 +3044,13 @@
         <v>5</v>
       </c>
       <c r="AV14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW14" t="n">
         <v>13</v>
       </c>
       <c r="AX14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY14" t="n">
         <v>1</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>12-24-2014-15</t>
+          <t>2014-12-24</t>
         </is>
       </c>
     </row>
@@ -3027,85 +3094,85 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E15" t="n">
         <v>9</v>
       </c>
       <c r="F15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G15" t="n">
-        <v>0.333</v>
+        <v>0.321</v>
       </c>
       <c r="H15" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="I15" t="n">
-        <v>38.5</v>
+        <v>38.1</v>
       </c>
       <c r="J15" t="n">
-        <v>87.40000000000001</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>0.441</v>
+        <v>0.438</v>
       </c>
       <c r="L15" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="M15" t="n">
-        <v>20</v>
+        <v>19.6</v>
       </c>
       <c r="N15" t="n">
-        <v>0.349</v>
+        <v>0.348</v>
       </c>
       <c r="O15" t="n">
-        <v>19.1</v>
+        <v>19.5</v>
       </c>
       <c r="P15" t="n">
-        <v>25.5</v>
+        <v>26</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.749</v>
+        <v>0.751</v>
       </c>
       <c r="R15" t="n">
         <v>12.1</v>
       </c>
       <c r="S15" t="n">
-        <v>30.4</v>
+        <v>30.2</v>
       </c>
       <c r="T15" t="n">
-        <v>42.5</v>
+        <v>42.3</v>
       </c>
       <c r="U15" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="V15" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="W15" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="X15" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Y15" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Z15" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="AA15" t="n">
         <v>21.6</v>
       </c>
-      <c r="AA15" t="n">
-        <v>21.3</v>
-      </c>
       <c r="AB15" t="n">
-        <v>103.1</v>
+        <v>102.6</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6</v>
+        <v>-6.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AE15" t="n">
         <v>25</v>
@@ -3117,10 +3184,10 @@
         <v>25</v>
       </c>
       <c r="AH15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AJ15" t="n">
         <v>2</v>
@@ -3129,7 +3196,7 @@
         <v>23</v>
       </c>
       <c r="AL15" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AM15" t="n">
         <v>21</v>
@@ -3138,34 +3205,34 @@
         <v>17</v>
       </c>
       <c r="AO15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP15" t="n">
         <v>6</v>
       </c>
       <c r="AQ15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR15" t="n">
         <v>5</v>
       </c>
       <c r="AS15" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AT15" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AU15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV15" t="n">
         <v>3</v>
       </c>
       <c r="AW15" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX15" t="n">
         <v>15</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>14</v>
       </c>
       <c r="AY15" t="n">
         <v>7</v>
@@ -3174,13 +3241,13 @@
         <v>20</v>
       </c>
       <c r="BA15" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB15" t="n">
         <v>12</v>
       </c>
-      <c r="BB15" t="n">
-        <v>10</v>
-      </c>
       <c r="BC15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>12-24-2014-15</t>
+          <t>2014-12-24</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>5</v>
       </c>
       <c r="AD16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AE16" t="n">
         <v>4</v>
@@ -3320,7 +3387,7 @@
         <v>15</v>
       </c>
       <c r="AO16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP16" t="n">
         <v>13</v>
@@ -3335,13 +3402,13 @@
         <v>14</v>
       </c>
       <c r="AT16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU16" t="n">
         <v>11</v>
       </c>
       <c r="AV16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW16" t="n">
         <v>11</v>
@@ -3350,7 +3417,7 @@
         <v>25</v>
       </c>
       <c r="AY16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ16" t="n">
         <v>7</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>12-24-2014-15</t>
+          <t>2014-12-24</t>
         </is>
       </c>
     </row>
@@ -3469,10 +3536,10 @@
         <v>-3.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF17" t="n">
         <v>17</v>
@@ -3490,13 +3557,13 @@
         <v>30</v>
       </c>
       <c r="AK17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AL17" t="n">
         <v>12</v>
       </c>
       <c r="AM17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN17" t="n">
         <v>14</v>
@@ -3520,7 +3587,7 @@
         <v>30</v>
       </c>
       <c r="AU17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AV17" t="n">
         <v>14</v>
@@ -3532,7 +3599,7 @@
         <v>30</v>
       </c>
       <c r="AY17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ17" t="n">
         <v>12</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>12-24-2014-15</t>
+          <t>2014-12-24</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-1.7</v>
       </c>
       <c r="AD18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE18" t="n">
         <v>14</v>
@@ -3660,7 +3727,7 @@
         <v>15</v>
       </c>
       <c r="AG18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH18" t="n">
         <v>6</v>
@@ -3717,7 +3784,7 @@
         <v>16</v>
       </c>
       <c r="AZ18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BA18" t="n">
         <v>16</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>12-24-2014-15</t>
+          <t>2014-12-24</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-10.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AE19" t="n">
         <v>27</v>
@@ -3851,7 +3918,7 @@
         <v>17</v>
       </c>
       <c r="AJ19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AK19" t="n">
         <v>24</v>
@@ -3881,7 +3948,7 @@
         <v>28</v>
       </c>
       <c r="AT19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AU19" t="n">
         <v>13</v>
@@ -3896,10 +3963,10 @@
         <v>24</v>
       </c>
       <c r="AY19" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AZ19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA19" t="n">
         <v>5</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>12-24-2014-15</t>
+          <t>2014-12-24</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F20" t="n">
         <v>14</v>
       </c>
       <c r="G20" t="n">
-        <v>0.481</v>
+        <v>0.5</v>
       </c>
       <c r="H20" t="n">
         <v>48.2</v>
@@ -3955,142 +4022,142 @@
         <v>39.1</v>
       </c>
       <c r="J20" t="n">
-        <v>84.90000000000001</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>0.46</v>
+        <v>0.458</v>
       </c>
       <c r="L20" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="M20" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="N20" t="n">
-        <v>0.338</v>
+        <v>0.335</v>
       </c>
       <c r="O20" t="n">
         <v>17</v>
       </c>
       <c r="P20" t="n">
-        <v>22.4</v>
+        <v>22.7</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.762</v>
+        <v>0.748</v>
       </c>
       <c r="R20" t="n">
-        <v>11.4</v>
+        <v>12</v>
       </c>
       <c r="S20" t="n">
-        <v>30.9</v>
+        <v>31.1</v>
       </c>
       <c r="T20" t="n">
-        <v>42.4</v>
+        <v>43.1</v>
       </c>
       <c r="U20" t="n">
         <v>21.8</v>
       </c>
       <c r="V20" t="n">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="W20" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X20" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Z20" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="AB20" t="n">
-        <v>101.9</v>
+        <v>101.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>-1</v>
+        <v>-0.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AE20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF20" t="n">
         <v>13</v>
       </c>
       <c r="AG20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH20" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AI20" t="n">
         <v>6</v>
       </c>
       <c r="AJ20" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AK20" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AL20" t="n">
         <v>25</v>
       </c>
       <c r="AM20" t="n">
+        <v>21</v>
+      </c>
+      <c r="AN20" t="n">
         <v>22</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>19</v>
       </c>
       <c r="AO20" t="n">
         <v>19</v>
       </c>
       <c r="AP20" t="n">
+        <v>19</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>17</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS20" t="n">
         <v>20</v>
       </c>
-      <c r="AQ20" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>9</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>21</v>
-      </c>
       <c r="AT20" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AU20" t="n">
         <v>14</v>
       </c>
       <c r="AV20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AW20" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AX20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AY20" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AZ20" t="n">
         <v>9</v>
       </c>
       <c r="BA20" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BB20" t="n">
         <v>14</v>
       </c>
       <c r="BC20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>12-24-2014-15</t>
+          <t>2014-12-24</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-6.2</v>
       </c>
       <c r="AD21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE21" t="n">
         <v>27</v>
@@ -4251,7 +4318,7 @@
         <v>16</v>
       </c>
       <c r="AV21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW21" t="n">
         <v>19</v>
@@ -4263,16 +4330,16 @@
         <v>2</v>
       </c>
       <c r="AZ21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BA21" t="n">
         <v>26</v>
       </c>
       <c r="BB21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BC21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>12-24-2014-15</t>
+          <t>2014-12-24</t>
         </is>
       </c>
     </row>
@@ -4379,10 +4446,10 @@
         <v>1.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF22" t="n">
         <v>17</v>
@@ -4403,7 +4470,7 @@
         <v>22</v>
       </c>
       <c r="AL22" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AM22" t="n">
         <v>14</v>
@@ -4415,13 +4482,13 @@
         <v>16</v>
       </c>
       <c r="AP22" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AQ22" t="n">
         <v>19</v>
       </c>
       <c r="AR22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS22" t="n">
         <v>6</v>
@@ -4436,10 +4503,10 @@
         <v>25</v>
       </c>
       <c r="AW22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AX22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY22" t="n">
         <v>18</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>12-24-2014-15</t>
+          <t>2014-12-24</t>
         </is>
       </c>
     </row>
@@ -4483,82 +4550,82 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E23" t="n">
         <v>11</v>
       </c>
       <c r="F23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G23" t="n">
-        <v>0.367</v>
+        <v>0.355</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
       </c>
       <c r="I23" t="n">
-        <v>36.7</v>
+        <v>36.5</v>
       </c>
       <c r="J23" t="n">
-        <v>80.3</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>0.457</v>
+        <v>0.454</v>
       </c>
       <c r="L23" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="M23" t="n">
-        <v>18.8</v>
+        <v>18.5</v>
       </c>
       <c r="N23" t="n">
         <v>0.375</v>
       </c>
       <c r="O23" t="n">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="P23" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.722</v>
+        <v>0.723</v>
       </c>
       <c r="R23" t="n">
-        <v>8.9</v>
+        <v>9.1</v>
       </c>
       <c r="S23" t="n">
-        <v>31.9</v>
+        <v>32.1</v>
       </c>
       <c r="T23" t="n">
-        <v>40.7</v>
+        <v>41.2</v>
       </c>
       <c r="U23" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="V23" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="W23" t="n">
         <v>6.6</v>
       </c>
       <c r="X23" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="Z23" t="n">
-        <v>20.6</v>
+        <v>20.8</v>
       </c>
       <c r="AA23" t="n">
         <v>18.9</v>
       </c>
       <c r="AB23" t="n">
-        <v>94.2</v>
+        <v>93.8</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5</v>
+        <v>-5.4</v>
       </c>
       <c r="AD23" t="n">
         <v>1</v>
@@ -4567,7 +4634,7 @@
         <v>21</v>
       </c>
       <c r="AF23" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AG23" t="n">
         <v>22</v>
@@ -4576,19 +4643,19 @@
         <v>28</v>
       </c>
       <c r="AI23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ23" t="n">
         <v>27</v>
       </c>
       <c r="AK23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AM23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AN23" t="n">
         <v>6</v>
@@ -4606,34 +4673,34 @@
         <v>27</v>
       </c>
       <c r="AS23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT23" t="n">
+        <v>22</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>29</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>22</v>
+      </c>
+      <c r="AW23" t="n">
         <v>25</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>28</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>20</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>23</v>
       </c>
       <c r="AX23" t="n">
         <v>29</v>
       </c>
       <c r="AY23" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AZ23" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BA23" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="BB23" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BC23" t="n">
         <v>25</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>12-24-2014-15</t>
+          <t>2014-12-24</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-11.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AE24" t="n">
         <v>30</v>
@@ -4788,7 +4855,7 @@
         <v>10</v>
       </c>
       <c r="AS24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT24" t="n">
         <v>20</v>
@@ -4806,7 +4873,7 @@
         <v>5</v>
       </c>
       <c r="AY24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ24" t="n">
         <v>23</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>12-24-2014-15</t>
+          <t>2014-12-24</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>1.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE25" t="n">
         <v>13</v>
@@ -4937,22 +5004,22 @@
         <v>13</v>
       </c>
       <c r="AH25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI25" t="n">
         <v>9</v>
       </c>
       <c r="AJ25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK25" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL25" t="n">
         <v>2</v>
       </c>
       <c r="AM25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AN25" t="n">
         <v>9</v>
@@ -4976,7 +5043,7 @@
         <v>17</v>
       </c>
       <c r="AU25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV25" t="n">
         <v>24</v>
@@ -4994,7 +5061,7 @@
         <v>26</v>
       </c>
       <c r="BA25" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BB25" t="n">
         <v>5</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>12-24-2014-15</t>
+          <t>2014-12-24</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>6.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -5182,7 +5249,7 @@
         <v>6</v>
       </c>
       <c r="BC26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>12-24-2014-15</t>
+          <t>2014-12-24</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-1.3</v>
       </c>
       <c r="AD27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AE27" t="n">
         <v>18</v>
@@ -5319,7 +5386,7 @@
         <v>29</v>
       </c>
       <c r="AN27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO27" t="n">
         <v>1</v>
@@ -5352,7 +5419,7 @@
         <v>28</v>
       </c>
       <c r="AY27" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AZ27" t="n">
         <v>24</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>12-24-2014-15</t>
+          <t>2014-12-24</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F28" t="n">
         <v>11</v>
       </c>
       <c r="G28" t="n">
-        <v>0.607</v>
+        <v>0.621</v>
       </c>
       <c r="H28" t="n">
         <v>49.4</v>
@@ -5411,52 +5478,52 @@
         <v>38.4</v>
       </c>
       <c r="J28" t="n">
-        <v>83.2</v>
+        <v>82.7</v>
       </c>
       <c r="K28" t="n">
-        <v>0.462</v>
+        <v>0.464</v>
       </c>
       <c r="L28" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="M28" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="N28" t="n">
-        <v>0.379</v>
+        <v>0.385</v>
       </c>
       <c r="O28" t="n">
-        <v>17.9</v>
+        <v>17.7</v>
       </c>
       <c r="P28" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.767</v>
+        <v>0.768</v>
       </c>
       <c r="R28" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="S28" t="n">
-        <v>34.9</v>
+        <v>34.7</v>
       </c>
       <c r="T28" t="n">
-        <v>45.1</v>
+        <v>44.8</v>
       </c>
       <c r="U28" t="n">
         <v>24.2</v>
       </c>
       <c r="V28" t="n">
-        <v>14.5</v>
+        <v>14.7</v>
       </c>
       <c r="W28" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="X28" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Z28" t="n">
         <v>19.3</v>
@@ -5465,13 +5532,13 @@
         <v>20.7</v>
       </c>
       <c r="AB28" t="n">
-        <v>103</v>
+        <v>102.9</v>
       </c>
       <c r="AC28" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AD28" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="AE28" t="n">
         <v>11</v>
@@ -5486,28 +5553,28 @@
         <v>1</v>
       </c>
       <c r="AI28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AJ28" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL28" t="n">
         <v>9</v>
       </c>
       <c r="AM28" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AN28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AO28" t="n">
         <v>13</v>
       </c>
       <c r="AP28" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AQ28" t="n">
         <v>13</v>
@@ -5519,22 +5586,22 @@
         <v>3</v>
       </c>
       <c r="AT28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU28" t="n">
         <v>6</v>
       </c>
       <c r="AV28" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW28" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AX28" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AY28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AZ28" t="n">
         <v>5</v>
@@ -5543,7 +5610,7 @@
         <v>18</v>
       </c>
       <c r="BB28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BC28" t="n">
         <v>8</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>12-24-2014-15</t>
+          <t>2014-12-24</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>8.1</v>
       </c>
       <c r="AD29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE29" t="n">
         <v>3</v>
@@ -5674,7 +5741,7 @@
         <v>12</v>
       </c>
       <c r="AK29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL29" t="n">
         <v>8</v>
@@ -5716,7 +5783,7 @@
         <v>19</v>
       </c>
       <c r="AY29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ29" t="n">
         <v>22</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>12-24-2014-15</t>
+          <t>2014-12-24</t>
         </is>
       </c>
     </row>
@@ -5835,13 +5902,13 @@
         <v>-4.8</v>
       </c>
       <c r="AD30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE30" t="n">
         <v>25</v>
       </c>
       <c r="AF30" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG30" t="n">
         <v>26</v>
@@ -5856,16 +5923,16 @@
         <v>29</v>
       </c>
       <c r="AK30" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM30" t="n">
         <v>20</v>
       </c>
       <c r="AN30" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO30" t="n">
         <v>15</v>
@@ -5883,7 +5950,7 @@
         <v>25</v>
       </c>
       <c r="AT30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU30" t="n">
         <v>24</v>
@@ -5898,7 +5965,7 @@
         <v>7</v>
       </c>
       <c r="AY30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ30" t="n">
         <v>3</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>12-24-2014-15</t>
+          <t>2014-12-24</t>
         </is>
       </c>
     </row>
@@ -6017,10 +6084,10 @@
         <v>3.3</v>
       </c>
       <c r="AD31" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AE31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF31" t="n">
         <v>7</v>
@@ -6029,13 +6096,13 @@
         <v>7</v>
       </c>
       <c r="AH31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI31" t="n">
         <v>8</v>
       </c>
       <c r="AJ31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK31" t="n">
         <v>5</v>
@@ -6053,7 +6120,7 @@
         <v>22</v>
       </c>
       <c r="AP31" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ31" t="n">
         <v>22</v>
@@ -6086,13 +6153,13 @@
         <v>21</v>
       </c>
       <c r="BA31" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BB31" t="n">
         <v>17</v>
       </c>
       <c r="BC31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>12-24-2014-15</t>
+          <t>2014-12-24</t>
         </is>
       </c>
     </row>
